--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/pre LAM_HRM-2031-0172/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/pre LAM_HRM-2031-0172/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
@@ -413,38 +413,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Distance 1</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
+          <t>Distance 2</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mean Stepheight</t>
+          <t>Angle</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Area</t>
         </is>
       </c>
     </row>
@@ -456,26 +446,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Fiducial 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.16858</v>
+        <v>122.99914</v>
       </c>
       <c r="D2" t="n">
-        <v>16.7191</v>
+        <v>86.89255</v>
       </c>
       <c r="E2" t="n">
-        <v>16.80507</v>
+        <v>91.13357999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>43.33642</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.05126</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.80448</v>
+        <v>533.24694</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +469,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.06412</v>
+        <v>123.20885</v>
       </c>
       <c r="D3" t="n">
-        <v>17.19079</v>
+        <v>87.40943</v>
       </c>
       <c r="E3" t="n">
-        <v>16.6654</v>
+        <v>93.68666</v>
       </c>
       <c r="F3" t="n">
-        <v>42.86298</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.05121</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.8573</v>
+        <v>522.4664</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +488,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.88636</v>
+        <v>125.69309</v>
       </c>
       <c r="D4" t="n">
-        <v>17.01955</v>
+        <v>87.27419999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>16.9678</v>
+        <v>90.58052000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>42.77509</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.05059</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.82474</v>
+        <v>529.28248</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +507,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.14423</v>
+        <v>123.57731</v>
       </c>
       <c r="D5" t="n">
-        <v>17.48369</v>
+        <v>87.37148000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>17.13389</v>
+        <v>93.0707</v>
       </c>
       <c r="F5" t="n">
-        <v>43.33271</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.0511</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.82624</v>
+        <v>525.38361</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +526,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.87823</v>
+        <v>123.33294</v>
       </c>
       <c r="D6" t="n">
-        <v>16.6448</v>
+        <v>89.72092000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>16.75584</v>
+        <v>91.7227</v>
       </c>
       <c r="F6" t="n">
-        <v>42.65493</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.05105</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.85315</v>
+        <v>520.4231</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +545,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.1452</v>
+        <v>120.99429</v>
       </c>
       <c r="D7" t="n">
-        <v>16.83865</v>
+        <v>87.66879</v>
       </c>
       <c r="E7" t="n">
-        <v>17.25661</v>
+        <v>92.92609</v>
       </c>
       <c r="F7" t="n">
-        <v>42.95408</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.05235</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.85311</v>
+        <v>516.28014</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +564,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.01218</v>
+        <v>124.95245</v>
       </c>
       <c r="D8" t="n">
-        <v>16.70915</v>
+        <v>86.45050999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>16.8911</v>
+        <v>89.42655000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>43.28836</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.05072</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.83692</v>
+        <v>531.87418</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +583,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.92812</v>
+        <v>123.93496</v>
       </c>
       <c r="D9" t="n">
-        <v>16.77989</v>
+        <v>88.23605000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>17.01557</v>
+        <v>92.84923000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>42.4562</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.05058</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.83348</v>
+        <v>522.79998</v>
       </c>
     </row>
     <row r="10">
@@ -660,712 +602,738 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.98062</v>
+        <v>123.88033</v>
       </c>
       <c r="D10" t="n">
-        <v>16.92784</v>
+        <v>88.64597999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>16.82747</v>
+        <v>92.93052</v>
       </c>
       <c r="F10" t="n">
-        <v>43.42897</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.05253</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.8337</v>
+        <v>520.97381</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Pad 2</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>16.76335</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.71723</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16.7049</v>
-      </c>
-      <c r="F11" t="n">
-        <v>43.62243</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05045</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.83091</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Micro Bump 3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.77456</v>
+        <v>8.79114</v>
       </c>
       <c r="D12" t="n">
-        <v>16.52913</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.99056</v>
-      </c>
-      <c r="F12" t="n">
-        <v>42.90547</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.05119</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.80889</v>
+        <v>24.46698</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.22503</v>
+        <v>8.657159999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>16.85023</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.82427</v>
-      </c>
-      <c r="F13" t="n">
-        <v>43.37752</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.05181</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.80882</v>
+        <v>24.76367</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.01705</v>
+        <v>8.714130000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>16.87947</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.63943</v>
-      </c>
-      <c r="F14" t="n">
-        <v>42.65996</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.05059</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.86641</v>
+        <v>24.0597</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.58558</v>
+        <v>8.73765</v>
       </c>
       <c r="D15" t="n">
-        <v>16.79062</v>
-      </c>
-      <c r="E15" t="n">
-        <v>17.1398</v>
-      </c>
-      <c r="F15" t="n">
-        <v>43.61467</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.04992</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.8332</v>
+        <v>25.15725</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.24151</v>
+        <v>8.5852</v>
       </c>
       <c r="D16" t="n">
-        <v>16.83532</v>
-      </c>
-      <c r="E16" t="n">
-        <v>17.29706</v>
-      </c>
-      <c r="F16" t="n">
-        <v>43.25662</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.05191</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.85437</v>
+        <v>24.49313</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.23271</v>
+        <v>8.70574</v>
       </c>
       <c r="D17" t="n">
-        <v>16.86818</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.82183</v>
-      </c>
-      <c r="F17" t="n">
-        <v>43.70812</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.05142</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.78287</v>
+        <v>24.76406</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.1639</v>
+        <v>8.64663</v>
       </c>
       <c r="D18" t="n">
-        <v>16.93592</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.83346</v>
-      </c>
-      <c r="F18" t="n">
-        <v>42.89061</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.05173</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.85705</v>
+        <v>24.90667</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>8.74099</v>
+      </c>
+      <c r="D19" t="n">
+        <v>24.44291</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>17.31457</v>
-      </c>
-      <c r="D19" t="n">
-        <v>16.92286</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17.03736</v>
-      </c>
-      <c r="F19" t="n">
-        <v>42.57732</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05008</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.84994</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" t="inlineStr">
+      <c r="C20" t="n">
+        <v>8.599539999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24.3299</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.62243</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.14079</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.615</v>
+        <v>17.48369</v>
       </c>
       <c r="D22" t="n">
-        <v>1.11574</v>
+        <v>17.13389</v>
+      </c>
+      <c r="E22" t="n">
+        <v>17.14423</v>
+      </c>
+      <c r="F22" t="n">
+        <v>43.33271</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0511</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.82624</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.6029099999999999</v>
+        <v>16.87823</v>
       </c>
       <c r="D23" t="n">
-        <v>1.1322</v>
+        <v>16.6448</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16.75584</v>
+      </c>
+      <c r="F23" t="n">
+        <v>42.65493</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.05105</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.85315</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.60476</v>
+        <v>17.25661</v>
       </c>
       <c r="D24" t="n">
-        <v>1.12483</v>
+        <v>16.83865</v>
+      </c>
+      <c r="E24" t="n">
+        <v>17.1452</v>
+      </c>
+      <c r="F24" t="n">
+        <v>42.95408</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.05235</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.85311</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.62842</v>
+        <v>17.01218</v>
       </c>
       <c r="D25" t="n">
-        <v>1.14895</v>
+        <v>16.70915</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.8911</v>
+      </c>
+      <c r="F25" t="n">
+        <v>43.28836</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.05072</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.83692</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.60543</v>
+        <v>17.01557</v>
       </c>
       <c r="D26" t="n">
-        <v>1.13405</v>
+        <v>16.77989</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.92812</v>
+      </c>
+      <c r="F26" t="n">
+        <v>42.4562</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.05058</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.83348</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.62437</v>
+        <v>16.98062</v>
       </c>
       <c r="D27" t="n">
-        <v>1.13557</v>
+        <v>16.82747</v>
+      </c>
+      <c r="E27" t="n">
+        <v>16.92784</v>
+      </c>
+      <c r="F27" t="n">
+        <v>43.42897</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.05253</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.8337</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.59672</v>
+        <v>16.76335</v>
       </c>
       <c r="D28" t="n">
-        <v>1.11899</v>
+        <v>16.7049</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16.71723</v>
+      </c>
+      <c r="F28" t="n">
+        <v>43.62243</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.05045</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.83091</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>16.99056</v>
+      </c>
+      <c r="D29" t="n">
+        <v>16.52913</v>
+      </c>
+      <c r="E29" t="n">
+        <v>16.77456</v>
+      </c>
+      <c r="F29" t="n">
+        <v>42.90547</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.05119</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.80889</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0.61124</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.12984</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
+      <c r="C30" t="n">
+        <v>17.22503</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16.82427</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.85023</v>
+      </c>
+      <c r="F30" t="n">
+        <v>43.37752</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.05181</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.80882</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Rz max</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Rz mean</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Rz min</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Rz max</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Ra mean</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Ra Std dev</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Ra min</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Ra max</t>
         </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>roughness</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.7646500000000001</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.08255</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.62871</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.9825</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.10962</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.00793</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.09232</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.12839</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.76409</v>
+        <v>0.75859</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08043</v>
+        <v>0.08234</v>
       </c>
       <c r="E32" t="n">
-        <v>0.61243</v>
+        <v>0.60507</v>
       </c>
       <c r="F32" t="n">
-        <v>0.96931</v>
+        <v>0.96493</v>
       </c>
       <c r="G32" t="n">
-        <v>0.11184</v>
+        <v>0.10928</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00775</v>
+        <v>0.00778</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09392</v>
+        <v>0.09192</v>
       </c>
       <c r="J32" t="n">
-        <v>0.12666</v>
+        <v>0.12798</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.74919</v>
+        <v>0.76869</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08247</v>
+        <v>0.08308</v>
       </c>
       <c r="E33" t="n">
-        <v>0.60881</v>
+        <v>0.59903</v>
       </c>
       <c r="F33" t="n">
-        <v>0.98007</v>
+        <v>0.96752</v>
       </c>
       <c r="G33" t="n">
-        <v>0.11055</v>
+        <v>0.11217</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00747</v>
+        <v>0.0077</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09501</v>
+        <v>0.09644</v>
       </c>
       <c r="J33" t="n">
-        <v>0.12652</v>
+        <v>0.12874</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.76433</v>
+        <v>0.7683</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08146</v>
+        <v>0.08241999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6017</v>
+        <v>0.62287</v>
       </c>
       <c r="F34" t="n">
-        <v>0.98178</v>
+        <v>0.97712</v>
       </c>
       <c r="G34" t="n">
-        <v>0.11145</v>
+        <v>0.11011</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00763</v>
+        <v>0.00781</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09462</v>
+        <v>0.09461</v>
       </c>
       <c r="J34" t="n">
-        <v>0.12986</v>
+        <v>0.12381</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.74274</v>
+        <v>0.76514</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08101999999999999</v>
+        <v>0.08261</v>
       </c>
       <c r="E35" t="n">
-        <v>0.61398</v>
+        <v>0.61213</v>
       </c>
       <c r="F35" t="n">
-        <v>0.95977</v>
+        <v>0.97014</v>
       </c>
       <c r="G35" t="n">
-        <v>0.10981</v>
+        <v>0.11174</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00787</v>
+        <v>0.00774</v>
       </c>
       <c r="I35" t="n">
-        <v>0.09594</v>
+        <v>0.09596</v>
       </c>
       <c r="J35" t="n">
-        <v>0.12847</v>
+        <v>0.12899</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.75784</v>
+        <v>0.7641</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08263</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6096200000000001</v>
+        <v>0.60095</v>
       </c>
       <c r="F36" t="n">
-        <v>0.98584</v>
+        <v>0.97636</v>
       </c>
       <c r="G36" t="n">
-        <v>0.11251</v>
+        <v>0.11204</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00773</v>
+        <v>0.00778</v>
       </c>
       <c r="I36" t="n">
-        <v>0.09328</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>0.12793</v>
+        <v>0.12679</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.75428</v>
+        <v>0.74359</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08189</v>
+        <v>0.08234</v>
       </c>
       <c r="E37" t="n">
-        <v>0.61883</v>
+        <v>0.60476</v>
       </c>
       <c r="F37" t="n">
-        <v>0.99037</v>
+        <v>0.97145</v>
       </c>
       <c r="G37" t="n">
-        <v>0.11114</v>
+        <v>0.11311</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00769</v>
+        <v>0.00783</v>
       </c>
       <c r="I37" t="n">
-        <v>0.09505</v>
+        <v>0.09283</v>
       </c>
       <c r="J37" t="n">
-        <v>0.12778</v>
+        <v>0.12887</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.7664800000000001</v>
+        <v>0.77006</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.08259</v>
       </c>
       <c r="E38" t="n">
-        <v>0.60711</v>
+        <v>0.59672</v>
       </c>
       <c r="F38" t="n">
-        <v>0.98144</v>
+        <v>0.9664</v>
       </c>
       <c r="G38" t="n">
-        <v>0.11232</v>
+        <v>0.11002</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00762</v>
+        <v>0.0077</v>
       </c>
       <c r="I38" t="n">
-        <v>0.09483</v>
+        <v>0.09506000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>0.12755</v>
+        <v>0.12898</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7754</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08273999999999999</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.60898</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.00487</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.10838</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12567</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>0.75046</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.07951999999999999</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.6163</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.981</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.10995</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.00763</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.09644999999999999</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.13174</v>
+      <c r="C40" t="n">
+        <v>0.7553299999999999</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08162999999999999</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.62132</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.98193</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.11026</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09314</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12886</v>
       </c>
     </row>
   </sheetData>
